--- a/Results/ClinVar/gene_level/top_decile_genes_across_plm_backgrounds.xlsx
+++ b/Results/ClinVar/gene_level/top_decile_genes_across_plm_backgrounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R112"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,34 +536,34 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.98</v>
+        <v>0.968</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.35</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.3666666666666666</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -594,19 +594,19 @@
         <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>0.97</v>
+        <v>0.966</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1047619047619046</v>
+        <v>0.1023809523809522</v>
       </c>
       <c r="I3" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -615,16 +615,16 @@
         <v>0.98</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.0166666666666666</v>
       </c>
       <c r="O3" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -639,53 +639,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MMACHC</t>
+          <t>GP1BA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.95</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1700000000000001</v>
+        <v>0.06593406593406601</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.96</v>
+        <v>0.6980000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.13</v>
+        <v>-0.0109890109890109</v>
       </c>
       <c r="O4" t="n">
-        <v>15</v>
+        <v>341</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
@@ -697,53 +697,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STING1</t>
+          <t>MMACHC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
-        <v>12</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.918</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1499999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="I5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2333333333333332</v>
+        <v>-0.04</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>414</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="b">
         <v>1</v>
@@ -755,53 +755,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOX5</t>
+          <t>KCNH1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="C6" t="n">
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9</v>
+        <v>0.8460000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1145833333333334</v>
+        <v>0.0997807017543859</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.8160000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0572916666666667</v>
+        <v>0.0592105263157894</v>
       </c>
       <c r="O6" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
@@ -813,50 +813,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ROBO4</t>
+          <t>SOX5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.89</v>
+        <v>0.8220000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1578947368421052</v>
+        <v>0.1041666666666667</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.03125</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
@@ -871,29 +871,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POT1</t>
+          <t>SOX9</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>0.85</v>
+        <v>0.7879999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.0982456140350878</v>
       </c>
       <c r="I8" t="n">
         <v>23</v>
@@ -902,19 +902,19 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0.73</v>
+        <v>0.6979999999999998</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08888888888888891</v>
+        <v>0.1298245614035087</v>
       </c>
       <c r="O8" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
@@ -929,53 +929,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KCNH1</t>
+          <t>ADGRG1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.84</v>
+        <v>0.786</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1063596491228069</v>
+        <v>0.0925925925925926</v>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0.84</v>
+        <v>0.5900000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0767543859649122</v>
+        <v>-0.0833333333333333</v>
       </c>
       <c r="O9" t="n">
-        <v>34</v>
+        <v>454</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
@@ -1000,40 +1000,40 @@
         <v>34</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.776</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08614800759013271</v>
+        <v>0.0603415559772295</v>
       </c>
       <c r="I10" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.73</v>
+        <v>0.734</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0461100569259963</v>
+        <v>0.0453510436432637</v>
       </c>
       <c r="O10" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="b">
         <v>1</v>
@@ -1045,50 +1045,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SOX9</t>
+          <t>GATA1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1000000000000002</v>
+        <v>0.1437499999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.72</v>
+        <v>0.784</v>
       </c>
       <c r="L11" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1350877192982457</v>
+        <v>0.0312499999999998</v>
       </c>
       <c r="O11" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -1103,53 +1103,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADGRG1</t>
+          <t>UROS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.79</v>
+        <v>0.708</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0.93</v>
+        <v>0.756</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.074074074074074</v>
+        <v>1.110223024625156e-16</v>
       </c>
       <c r="O12" t="n">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="P12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
@@ -1161,53 +1161,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GATA1</t>
+          <t>STING1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.79</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.15625</v>
+        <v>0.0499999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.624</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0437499999999999</v>
+        <v>0.09999999999999989</v>
       </c>
       <c r="O13" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="P13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
@@ -1219,50 +1219,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GP1BA</t>
+          <t>FGFR3</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>0.96</v>
+        <v>0.6719999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0533088235294118</v>
       </c>
       <c r="I14" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0.75</v>
+        <v>0.674</v>
       </c>
       <c r="L14" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M14" t="b">
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0219780219780221</v>
+        <v>-0.0036764705882352</v>
       </c>
       <c r="O14" t="n">
-        <v>145</v>
+        <v>308</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1290,37 +1290,37 @@
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.96</v>
+        <v>0.8959999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.0261904761904762</v>
       </c>
       <c r="I15" t="n">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.96</v>
+        <v>0.844</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M15" t="b">
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0404761904761904</v>
+        <v>0.0142857142857142</v>
       </c>
       <c r="O15" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -1348,40 +1348,40 @@
         <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0262923351158644</v>
+        <v>0.0147058823529412</v>
       </c>
       <c r="I16" t="n">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M16" t="b">
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.032976827094474</v>
+        <v>0.0334224598930481</v>
       </c>
       <c r="O16" t="n">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="P16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
@@ -1393,53 +1393,53 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EMD</t>
+          <t>ROBO4</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8</v>
+        <v>0.778</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0399999999999999</v>
+        <v>0.0350877192982456</v>
       </c>
       <c r="I17" t="n">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="L17" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0599999999999999</v>
+        <v>0.0263157894736841</v>
       </c>
       <c r="O17" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="P17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
@@ -1451,50 +1451,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KRIT1</t>
+          <t>MLC1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8</v>
+        <v>0.748</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0250000000000001</v>
+        <v>-0.0294117647058823</v>
       </c>
       <c r="I18" t="n">
-        <v>154</v>
+        <v>413</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.89</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="M18" t="b">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.0490196078431373</v>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -1509,166 +1509,166 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EZH2</t>
+          <t>POT1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.99</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1717171717171717</v>
+        <v>0.0222222222222222</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="L19" t="n">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="M19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0033670033670034</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="O19" t="n">
-        <v>281</v>
+        <v>15</v>
       </c>
       <c r="P19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FOXG1</t>
+          <t>EMD</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.99</v>
+        <v>0.6679999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1215238095238095</v>
+        <v>0.0199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.632</v>
       </c>
       <c r="L20" t="n">
-        <v>133</v>
+        <v>40</v>
       </c>
       <c r="M20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.003047619047619</v>
+        <v>0.0399999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>284</v>
+        <v>28</v>
       </c>
       <c r="P20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IRF2BPL</t>
+          <t>FOXG1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="E21" t="n">
-        <v>0.98</v>
+        <v>0.976</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2461538461538462</v>
+        <v>0.12</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.418</v>
       </c>
       <c r="L21" t="n">
-        <v>384</v>
+        <v>110</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.0017142857142857</v>
       </c>
       <c r="O21" t="n">
-        <v>384</v>
+        <v>291</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
@@ -1683,50 +1683,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>IRF2BPL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>0.96</v>
+        <v>0.976</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1742574257425743</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>205</v>
+        <v>399</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0039603960396039</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>268</v>
+        <v>182</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
@@ -1754,37 +1754,37 @@
         <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>0.96</v>
+        <v>0.952</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2085561497326202</v>
+        <v>0.2058823529411764</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>0.4720000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="M23" t="b">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0481283422459892</v>
+        <v>0.016042780748663</v>
       </c>
       <c r="O23" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
@@ -1812,19 +1812,19 @@
         <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>0.95</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2181818181818182</v>
+        <v>0.2090909090909091</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="M24" t="b">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>448</v>
+        <v>242</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
@@ -1857,50 +1857,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PTPN11</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C25" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="F25" t="n">
         <v>8</v>
       </c>
-      <c r="E25" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F25" t="n">
-        <v>14</v>
-      </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1085164835164835</v>
+        <v>0.1683168316831683</v>
       </c>
       <c r="I25" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0.39</v>
+        <v>0.208</v>
       </c>
       <c r="L25" t="n">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0054945054945054</v>
+        <v>-0.0039603960396039</v>
       </c>
       <c r="O25" t="n">
-        <v>256</v>
+        <v>313</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
@@ -1915,50 +1915,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CNOT3</t>
+          <t>EZH2</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C26" t="n">
+        <v>27</v>
+      </c>
+      <c r="D26" t="n">
+        <v>22</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1616161616161616</v>
+      </c>
+      <c r="I26" t="n">
         <v>8</v>
       </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F26" t="n">
-        <v>16</v>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I26" t="n">
-        <v>24</v>
-      </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.24</v>
+        <v>0.272</v>
       </c>
       <c r="L26" t="n">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.015625</v>
+        <v>-0.0016835016835016</v>
       </c>
       <c r="O26" t="n">
-        <v>180</v>
+        <v>290</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
@@ -1973,50 +1973,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PCYT1A</t>
+          <t>PTPN11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>0.87</v>
+        <v>0.912</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.1057692307692308</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="L27" t="n">
-        <v>414</v>
+        <v>184</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>-0.0329670329670329</v>
       </c>
       <c r="O27" t="n">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -2044,16 +2044,16 @@
         <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>0.87</v>
+        <v>0.8460000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1965811965811965</v>
+        <v>0.1538461538461537</v>
       </c>
       <c r="I28" t="n">
         <v>9</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
@@ -2074,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>415</v>
+        <v>207</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
@@ -2089,53 +2089,53 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RALA</t>
+          <t>AFG3L2</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>0.85</v>
+        <v>0.7899999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.05</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.65</v>
+        <v>0.462</v>
       </c>
       <c r="L29" t="n">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0625</v>
+        <v>0.0428571428571429</v>
       </c>
       <c r="O29" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="P29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -2147,50 +2147,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AFG3L2</t>
+          <t>ASL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C30" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.84</v>
+        <v>0.784</v>
       </c>
       <c r="F30" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0857142857142856</v>
+        <v>0.0524590163934426</v>
       </c>
       <c r="I30" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>0.458</v>
       </c>
       <c r="L30" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0571428571428571</v>
+        <v>-0.0131147540983606</v>
       </c>
       <c r="O30" t="n">
-        <v>56</v>
+        <v>349</v>
       </c>
       <c r="P30" t="b">
         <v>0</v>
@@ -2205,50 +2205,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GARS1</t>
+          <t>CNOT3</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.7660000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1443850267379679</v>
+        <v>0.09375</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0.42</v>
+        <v>0.144</v>
       </c>
       <c r="L31" t="n">
-        <v>144</v>
+        <v>267</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.016042780748663</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="P31" t="b">
         <v>0</v>
@@ -2263,50 +2263,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KCNC3</t>
+          <t>PCYT1A</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>14</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="F32" t="n">
+        <v>28</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1904761904761904</v>
+      </c>
+      <c r="I32" t="n">
         <v>5</v>
       </c>
-      <c r="D32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="F32" t="n">
-        <v>40</v>
-      </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I32" t="n">
-        <v>17</v>
-      </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>201</v>
+        <v>421</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0249999999999999</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="P32" t="b">
         <v>0</v>
@@ -2321,50 +2321,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RLIM</t>
+          <t>RALA</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>14</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="F33" t="n">
+        <v>29</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I33" t="n">
         <v>15</v>
       </c>
-      <c r="C33" t="n">
-        <v>7</v>
-      </c>
-      <c r="D33" t="n">
-        <v>8</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F33" t="n">
-        <v>43</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.1607142857142857</v>
-      </c>
-      <c r="I33" t="n">
-        <v>14</v>
-      </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>0.414</v>
       </c>
       <c r="L33" t="n">
-        <v>427</v>
+        <v>113</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="O33" t="n">
-        <v>427</v>
+        <v>51</v>
       </c>
       <c r="P33" t="b">
         <v>0</v>
@@ -2379,99 +2379,99 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WDR45</t>
+          <t>PRKAG2</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D34" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>0.99</v>
+        <v>0.7460000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0227272727272727</v>
+        <v>0.0470588235294118</v>
       </c>
       <c r="I34" t="n">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="J34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>137</v>
+        <v>429</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0710227272727272</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="P34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
       <c r="R34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SLC4A1</t>
+          <t>RLIM</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C35" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
         <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>0.96</v>
+        <v>0.744</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0394736842105263</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="I35" t="n">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="J35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>438</v>
+        <v>219</v>
       </c>
       <c r="P35" t="b">
         <v>0</v>
@@ -2489,56 +2489,56 @@
         <v>0</v>
       </c>
       <c r="R35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GNAO1</t>
+          <t>GARS1</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C36" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="D36" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
       <c r="F36" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0178571428571429</v>
+        <v>0.1336898395721926</v>
       </c>
       <c r="I36" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="J36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.38</v>
+        <v>0.342</v>
       </c>
       <c r="L36" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0123626373626373</v>
+        <v>-0.0106951871657754</v>
       </c>
       <c r="O36" t="n">
-        <v>207</v>
+        <v>338</v>
       </c>
       <c r="P36" t="b">
         <v>0</v>
@@ -2547,56 +2547,56 @@
         <v>0</v>
       </c>
       <c r="R36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COL10A1</t>
+          <t>GPR143</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C37" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>0.91</v>
+        <v>0.698</v>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0512820512820512</v>
+        <v>0.0454545454545454</v>
       </c>
       <c r="I37" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="J37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.28</v>
+        <v>0.364</v>
       </c>
       <c r="L37" t="n">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.0064102564102564</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="O37" t="n">
-        <v>250</v>
+        <v>442</v>
       </c>
       <c r="P37" t="b">
         <v>0</v>
@@ -2605,56 +2605,56 @@
         <v>0</v>
       </c>
       <c r="R37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SPG7</t>
+          <t>GFAP</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C38" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D38" t="n">
         <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9</v>
+        <v>0.696</v>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0625</v>
+        <v>0.0452127659574468</v>
       </c>
       <c r="I38" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="J38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.015625</v>
+        <v>0.007978723404255299</v>
       </c>
       <c r="O38" t="n">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="P38" t="b">
         <v>0</v>
@@ -2663,56 +2663,56 @@
         <v>0</v>
       </c>
       <c r="R38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EBF3</t>
+          <t>CYP11B2</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E39" t="n">
-        <v>0.87</v>
+        <v>0.6719999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.04</v>
+        <v>0.050595238095238</v>
       </c>
       <c r="I39" t="n">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="J39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.026</v>
       </c>
       <c r="L39" t="n">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0.02</v>
+        <v>-0.0029761904761905</v>
       </c>
       <c r="O39" t="n">
-        <v>155</v>
+        <v>303</v>
       </c>
       <c r="P39" t="b">
         <v>0</v>
@@ -2721,56 +2721,56 @@
         <v>0</v>
       </c>
       <c r="R39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FUS</t>
+          <t>COL10A1</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C40" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E40" t="n">
-        <v>0.87</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0510204081632653</v>
+        <v>0.0363247863247863</v>
       </c>
       <c r="I40" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.254</v>
       </c>
       <c r="L40" t="n">
-        <v>359</v>
+        <v>209</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>-0.0064102564102563</v>
       </c>
       <c r="O40" t="n">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="P40" t="b">
         <v>0</v>
@@ -2785,53 +2785,53 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TUBB2A</t>
+          <t>SPAST</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>0.87</v>
+        <v>0.8539999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.08444444444444429</v>
+        <v>0.0394889663182346</v>
       </c>
       <c r="I41" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.4</v>
+        <v>0.066</v>
       </c>
       <c r="L41" t="n">
-        <v>155</v>
+        <v>311</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0666666666666666</v>
+        <v>-0.0005807200929152</v>
       </c>
       <c r="O41" t="n">
-        <v>46</v>
+        <v>280</v>
       </c>
       <c r="P41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="b">
         <v>0</v>
@@ -2843,20 +2843,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TUBB2A</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="D42" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="F42" t="n">
         <v>27</v>
@@ -2865,28 +2865,28 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0149773598049461</v>
+        <v>0.0399999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>213</v>
+        <v>49</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>0.458</v>
       </c>
       <c r="L42" t="n">
-        <v>320</v>
+        <v>95</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>-0.06666666666666669</v>
       </c>
       <c r="O42" t="n">
-        <v>320</v>
+        <v>441</v>
       </c>
       <c r="P42" t="b">
         <v>0</v>
@@ -2901,50 +2901,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DCLRE1C</t>
+          <t>SLC6A1</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="C43" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="D43" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="E43" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="F43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0576923076923078</v>
+        <v>0.0387840670859538</v>
       </c>
       <c r="I43" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.66</v>
+        <v>0.276</v>
       </c>
       <c r="L43" t="n">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.0448717948717949</v>
+        <v>0.0031446540880502</v>
       </c>
       <c r="O43" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="P43" t="b">
         <v>0</v>
@@ -2959,50 +2959,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SPAST</t>
+          <t>SPG7</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>137</v>
+        <v>24</v>
       </c>
       <c r="C44" t="n">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="D44" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0412311265969803</v>
+        <v>0.0390625</v>
       </c>
       <c r="I44" t="n">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.11</v>
+        <v>0.304</v>
       </c>
       <c r="L44" t="n">
-        <v>281</v>
+        <v>170</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0005807200929152</v>
+        <v>-0.0078125</v>
       </c>
       <c r="O44" t="n">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="P44" t="b">
         <v>0</v>
@@ -3017,20 +3017,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MAPT</t>
+          <t>GNAO1</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C45" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D45" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.744</v>
       </c>
       <c r="F45" t="n">
         <v>34</v>
@@ -3039,28 +3039,28 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0401337792642141</v>
+        <v>-0.0178571428571429</v>
       </c>
       <c r="I45" t="n">
-        <v>104</v>
+        <v>388</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.362</v>
       </c>
       <c r="L45" t="n">
-        <v>398</v>
+        <v>148</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-0.0096153846153846</v>
       </c>
       <c r="O45" t="n">
-        <v>398</v>
+        <v>334</v>
       </c>
       <c r="P45" t="b">
         <v>0</v>
@@ -3075,20 +3075,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PRKAG2</t>
+          <t>SRD5A2</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C46" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="F46" t="n">
         <v>36</v>
@@ -3097,28 +3097,28 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0529411764705882</v>
+        <v>0.0282258064516128</v>
       </c>
       <c r="I46" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>0.302</v>
       </c>
       <c r="L46" t="n">
-        <v>424</v>
+        <v>171</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>-0.0201612903225806</v>
       </c>
       <c r="O46" t="n">
-        <v>424</v>
+        <v>376</v>
       </c>
       <c r="P46" t="b">
         <v>0</v>
@@ -3133,53 +3133,53 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ACTN4</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0333333333333332</v>
+        <v>0.0006966213862765</v>
       </c>
       <c r="I47" t="n">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.71</v>
+        <v>0.002</v>
       </c>
       <c r="L47" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0.08888888888888891</v>
+        <v>-0.0010449320794149</v>
       </c>
       <c r="O47" t="n">
-        <v>28</v>
+        <v>283</v>
       </c>
       <c r="P47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
@@ -3191,20 +3191,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SLC6A1</t>
+          <t>WDR45</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="C48" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="D48" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="E48" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="F48" t="n">
         <v>47</v>
@@ -3213,31 +3213,31 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0443745632424877</v>
+        <v>0.0113636363636362</v>
       </c>
       <c r="I48" t="n">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.28</v>
+        <v>0.504</v>
       </c>
       <c r="L48" t="n">
-        <v>220</v>
+        <v>75</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0.0034940600978337</v>
+        <v>0.03125</v>
       </c>
       <c r="O48" t="n">
-        <v>278</v>
+        <v>36</v>
       </c>
       <c r="P48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="b">
         <v>0</v>
@@ -3249,53 +3249,53 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MLC1</t>
+          <t>MMUT</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="C49" t="n">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="D49" t="n">
         <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>0.77</v>
+        <v>0.652</v>
       </c>
       <c r="F49" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G49" t="b">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.06862745098039209</v>
+        <v>0.06818181818181809</v>
       </c>
       <c r="I49" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.1119999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>50</v>
+        <v>285</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0.07843137254901961</v>
+        <v>0.0045454545454545</v>
       </c>
       <c r="O49" t="n">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="P49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
@@ -3307,53 +3307,53 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CNGB3</t>
+          <t>PORCN</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>0.73</v>
+        <v>0.642</v>
       </c>
       <c r="F50" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0285714285714286</v>
+        <v>-0.0341880341880342</v>
       </c>
       <c r="I50" t="n">
-        <v>138</v>
+        <v>425</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0.79</v>
+        <v>0.646</v>
       </c>
       <c r="L50" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M50" t="b">
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>0.0499999999999999</v>
+        <v>0.0256410256410255</v>
       </c>
       <c r="O50" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="P50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
@@ -3365,50 +3365,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FOXH1</t>
+          <t>MSH2</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>11</v>
+        <v>341</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>232</v>
       </c>
       <c r="E51" t="n">
-        <v>0.73</v>
+        <v>0.5900000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G51" t="b">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.09999999999999989</v>
+        <v>0.0472951597595697</v>
       </c>
       <c r="I51" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="L51" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="M51" t="b">
         <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.0520404935147105</v>
       </c>
       <c r="O51" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
@@ -3436,37 +3436,37 @@
         <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>0.72</v>
+        <v>0.588</v>
       </c>
       <c r="F52" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1</v>
+        <v>0.0555555555555555</v>
       </c>
       <c r="I52" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="L52" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.110223024625156e-16</v>
+        <v>-0.0555555555555555</v>
       </c>
       <c r="O52" t="n">
-        <v>307</v>
+        <v>433</v>
       </c>
       <c r="P52" t="b">
         <v>0</v>
@@ -3481,53 +3481,53 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DNAI1</t>
+          <t>FOXH1</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>0.72</v>
+        <v>0.584</v>
       </c>
       <c r="F53" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0277777777777777</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="I53" t="n">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0.25</v>
+        <v>0.742</v>
       </c>
       <c r="L53" t="n">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="M53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>0.06944444444444441</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="P53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="b">
         <v>0</v>
@@ -3539,53 +3539,53 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GATA2</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52</v>
+        <v>171</v>
       </c>
       <c r="C54" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="E54" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="F54" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0972972972972973</v>
+        <v>0.0363636363636362</v>
       </c>
       <c r="I54" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="J54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>0.5959999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>362</v>
+        <v>46</v>
       </c>
       <c r="M54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.0366616989567808</v>
       </c>
       <c r="O54" t="n">
-        <v>362</v>
+        <v>31</v>
       </c>
       <c r="P54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
@@ -3597,53 +3597,53 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TNPO2</t>
+          <t>KIF22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C55" t="n">
         <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.572</v>
       </c>
       <c r="F55" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.06666666666666669</v>
+        <v>0.0686274509803922</v>
       </c>
       <c r="I55" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>0.14</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>268</v>
+        <v>53</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0.1</v>
+        <v>0.0196078431372548</v>
       </c>
       <c r="O55" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="P55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="b">
         <v>0</v>
@@ -3655,50 +3655,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GPI</t>
+          <t>OPA1</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>0.67</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.0155490767735666</v>
       </c>
       <c r="I56" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.79</v>
+        <v>0.462</v>
       </c>
       <c r="L56" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="M56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0.1777777777777777</v>
+        <v>0.0281827016520894</v>
       </c>
       <c r="O56" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
@@ -3713,53 +3713,53 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LHCGR</t>
+          <t>CNGB3</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E57" t="n">
-        <v>0.67</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G57" t="b">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.0214285714285713</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>401</v>
       </c>
       <c r="J57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.89</v>
+        <v>0.6819999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>0.09999999999999989</v>
+        <v>-0.0428571428571429</v>
       </c>
       <c r="O57" t="n">
-        <v>23</v>
+        <v>417</v>
       </c>
       <c r="P57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
@@ -3771,50 +3771,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MMUT</t>
+          <t>MTHFR</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="C58" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="D58" t="n">
         <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>0.66</v>
+        <v>0.5520000000000002</v>
       </c>
       <c r="F58" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G58" t="b">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.08484848484848501</v>
+        <v>0.075</v>
       </c>
       <c r="I58" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0.09</v>
+        <v>0.226</v>
       </c>
       <c r="L58" t="n">
-        <v>286</v>
+        <v>225</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0.0015151515151514</v>
+        <v>-0.0166666666666667</v>
       </c>
       <c r="O58" t="n">
-        <v>290</v>
+        <v>362</v>
       </c>
       <c r="P58" t="b">
         <v>0</v>
@@ -3829,53 +3829,53 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>UROS</t>
+          <t>GATA2</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E59" t="n">
-        <v>0.65</v>
+        <v>0.5459999999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G59" t="b">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.09009009009009</v>
       </c>
       <c r="I59" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>23</v>
+        <v>382</v>
       </c>
       <c r="M59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="P59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
@@ -3887,50 +3887,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PROM1</t>
+          <t>KRIT1</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>13</v>
       </c>
       <c r="C60" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" t="n">
         <v>8</v>
       </c>
-      <c r="D60" t="n">
-        <v>5</v>
-      </c>
       <c r="E60" t="n">
-        <v>0.63</v>
+        <v>0.538</v>
       </c>
       <c r="F60" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.09999999999999989</v>
+        <v>-0.0749999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>37</v>
+        <v>453</v>
       </c>
       <c r="J60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.42</v>
+        <v>0.658</v>
       </c>
       <c r="L60" t="n">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="M60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>0.0499999999999999</v>
+        <v>-0.09999999999999989</v>
       </c>
       <c r="O60" t="n">
-        <v>70</v>
+        <v>461</v>
       </c>
       <c r="P60" t="b">
         <v>0</v>
@@ -3945,53 +3945,53 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GTPBP3</t>
+          <t>DCLRE1C</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6</v>
+        <v>0.532</v>
       </c>
       <c r="F61" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G61" t="b">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0448717948717949</v>
       </c>
       <c r="I61" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0.63</v>
+        <v>0.4019999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0.0749999999999999</v>
+        <v>-0.0320512820512821</v>
       </c>
       <c r="O61" t="n">
-        <v>35</v>
+        <v>402</v>
       </c>
       <c r="P61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -4003,53 +4003,53 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CAMK2B</t>
+          <t>PDE6C</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C62" t="n">
+        <v>11</v>
+      </c>
+      <c r="D62" t="n">
         <v>5</v>
       </c>
-      <c r="D62" t="n">
-        <v>57</v>
-      </c>
       <c r="E62" t="n">
-        <v>0.59</v>
+        <v>0.528</v>
       </c>
       <c r="F62" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G62" t="b">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0210526315789475</v>
+        <v>0.1272727272727272</v>
       </c>
       <c r="I62" t="n">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="J62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0.37</v>
+        <v>0.368</v>
       </c>
       <c r="L62" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0.087719298245614</v>
+        <v>0.018181818181818</v>
       </c>
       <c r="O62" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="b">
         <v>0</v>
@@ -4061,50 +4061,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MSH2</t>
+          <t>PADI6</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>341</v>
+        <v>12</v>
       </c>
       <c r="C63" t="n">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>232</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>0.59</v>
+        <v>0.526</v>
       </c>
       <c r="F63" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0528313824739007</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="I63" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="J63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0.74</v>
+        <v>0.136</v>
       </c>
       <c r="L63" t="n">
-        <v>42</v>
+        <v>271</v>
       </c>
       <c r="M63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0.0537409047769692</v>
+        <v>-0.0571428571428571</v>
       </c>
       <c r="O63" t="n">
-        <v>64</v>
+        <v>436</v>
       </c>
       <c r="P63" t="b">
         <v>0</v>
@@ -4119,53 +4119,53 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GRIN1</t>
+          <t>GLDC</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C64" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D64" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.5240000000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G64" t="b">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0491803278688526</v>
+        <v>0.0779914529914528</v>
       </c>
       <c r="I64" t="n">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="J64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0.6</v>
+        <v>0.344</v>
       </c>
       <c r="L64" t="n">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0.07240437158469951</v>
+        <v>-0.0512820512820513</v>
       </c>
       <c r="O64" t="n">
-        <v>37</v>
+        <v>430</v>
       </c>
       <c r="P64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
@@ -4177,53 +4177,53 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KIF22</t>
+          <t>LHCGR</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D65" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.524</v>
       </c>
       <c r="F65" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G65" t="b">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.08823529411764711</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="I65" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="J65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0.51</v>
+        <v>0.784</v>
       </c>
       <c r="L65" t="n">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="M65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>0.0490196078431373</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="O65" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="P65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
@@ -4235,50 +4235,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MTHFR</t>
+          <t>PRSS1</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C66" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.5200000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1</v>
+        <v>0.1238095238095237</v>
       </c>
       <c r="I66" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0.16</v>
+        <v>0.506</v>
       </c>
       <c r="L66" t="n">
-        <v>258</v>
+        <v>74</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0.0333333333333333</v>
+        <v>-0.1142857142857144</v>
       </c>
       <c r="O66" t="n">
-        <v>110</v>
+        <v>463</v>
       </c>
       <c r="P66" t="b">
         <v>0</v>
@@ -4293,53 +4293,53 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PADI6</t>
+          <t>GRIN1</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.514</v>
       </c>
       <c r="F67" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G67" t="b">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1999999999999999</v>
+        <v>0.0396174863387979</v>
       </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="J67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.22</v>
+        <v>0.64</v>
       </c>
       <c r="L67" t="n">
-        <v>238</v>
+        <v>38</v>
       </c>
       <c r="M67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>0.0285714285714286</v>
+        <v>0.0573770491803279</v>
       </c>
       <c r="O67" t="n">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="P67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
@@ -4351,50 +4351,50 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PDE6C</t>
+          <t>TP63</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C68" t="n">
+        <v>57</v>
+      </c>
+      <c r="D68" t="n">
         <v>11</v>
       </c>
-      <c r="D68" t="n">
-        <v>5</v>
-      </c>
       <c r="E68" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.506</v>
       </c>
       <c r="F68" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="G68" t="b">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.0159489633173843</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="J68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.47</v>
+        <v>0.614</v>
       </c>
       <c r="L68" t="n">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="M68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>0.0909090909090908</v>
+        <v>0.0287081339712917</v>
       </c>
       <c r="O68" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -4409,53 +4409,53 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PPP2R5D</t>
+          <t>CAMK2B</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C69" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="E69" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.502</v>
       </c>
       <c r="F69" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G69" t="b">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0923076923076924</v>
+        <v>-0.0245614035087718</v>
       </c>
       <c r="I69" t="n">
-        <v>40</v>
+        <v>408</v>
       </c>
       <c r="J69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.91</v>
+        <v>0.354</v>
       </c>
       <c r="L69" t="n">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="M69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0.0461538461538462</v>
+        <v>0.0771929824561403</v>
       </c>
       <c r="O69" t="n">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="P69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" t="b">
         <v>0</v>
@@ -4467,53 +4467,53 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IL7R</t>
+          <t>PPP2R5D</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D70" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F70" t="n">
+        <v>101</v>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.0461538461538462</v>
+      </c>
+      <c r="I70" t="n">
+        <v>43</v>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.7580000000000001</v>
+      </c>
+      <c r="L70" t="n">
         <v>17</v>
       </c>
-      <c r="E70" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F70" t="n">
-        <v>110</v>
-      </c>
-      <c r="G70" t="b">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.0588235294117647</v>
-      </c>
-      <c r="I70" t="n">
-        <v>68</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L70" t="n">
-        <v>41</v>
-      </c>
       <c r="M70" t="b">
         <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>0.0718954248366013</v>
+        <v>0.0153846153846154</v>
       </c>
       <c r="O70" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="P70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="b">
         <v>0</v>
@@ -4525,53 +4525,53 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PRSS1</t>
+          <t>EPHB4</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D71" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="E71" t="n">
-        <v>0.53</v>
+        <v>0.4859999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G71" t="b">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0104364326375712</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="J71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.362</v>
       </c>
       <c r="L71" t="n">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c r="M71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0.0190476190476189</v>
+        <v>0.0256166982922201</v>
       </c>
       <c r="O71" t="n">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="P71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
@@ -4583,53 +4583,53 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KCND2</t>
+          <t>IL7R</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D72" t="n">
+        <v>17</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="F72" t="n">
+        <v>107</v>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.0130718954248365</v>
+      </c>
+      <c r="I72" t="n">
+        <v>369</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="L72" t="n">
         <v>11</v>
       </c>
-      <c r="E72" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F72" t="n">
-        <v>113</v>
-      </c>
-      <c r="G72" t="b">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.2545454545454544</v>
-      </c>
-      <c r="I72" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" t="b">
-        <v>1</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>386</v>
-      </c>
       <c r="M72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>0.0522875816993464</v>
       </c>
       <c r="O72" t="n">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="P72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" t="b">
         <v>0</v>
@@ -4641,50 +4641,50 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CDH1</t>
+          <t>RAG2</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="C73" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D73" t="n">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="E73" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="F73" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G73" t="b">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.015862524785195</v>
+        <v>0.0226757369614513</v>
       </c>
       <c r="I73" t="n">
-        <v>203</v>
+        <v>75</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.9</v>
+        <v>0.57</v>
       </c>
       <c r="L73" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="M73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0.2432253800396563</v>
+        <v>0.0408163265306122</v>
       </c>
       <c r="O73" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -4699,53 +4699,53 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MAK</t>
+          <t>GPI</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>0.5</v>
+        <v>0.4640000000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="G74" t="b">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0238095238095237</v>
+        <v>0.0222222222222222</v>
       </c>
       <c r="I74" t="n">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="L74" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="M74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>0.0714285714285714</v>
+        <v>-0.0222222222222222</v>
       </c>
       <c r="O74" t="n">
-        <v>39</v>
+        <v>381</v>
       </c>
       <c r="P74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="b">
         <v>0</v>
@@ -4757,50 +4757,50 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ALOXE3</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>0.49</v>
+        <v>0.4619999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="G75" t="b">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0999999999999998</v>
+        <v>0.0185185185185184</v>
       </c>
       <c r="I75" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="J75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="L75" t="n">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.0555555555555555</v>
       </c>
       <c r="O75" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -4815,50 +4815,50 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GLDC</t>
+          <t>RPE65</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C76" t="n">
         <v>78</v>
       </c>
       <c r="D76" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>0.45</v>
+        <v>0.444</v>
       </c>
       <c r="F76" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G76" t="b">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0908119658119657</v>
+        <v>0.0149572649572649</v>
       </c>
       <c r="I76" t="n">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="J76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.32</v>
+        <v>0.6679999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>199</v>
+        <v>32</v>
       </c>
       <c r="M76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>0.0149572649572649</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="P76" t="b">
         <v>0</v>
@@ -4873,50 +4873,50 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ZMYND11</t>
+          <t>DNAI1</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D77" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E77" t="n">
-        <v>0.42</v>
+        <v>0.434</v>
       </c>
       <c r="F77" t="n">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="G77" t="b">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="L77" t="n">
-        <v>31</v>
+        <v>234</v>
       </c>
       <c r="M77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0.1928571428571429</v>
+        <v>0.0277777777777777</v>
       </c>
       <c r="O77" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -4931,32 +4931,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CCN6</t>
+          <t>KCND2</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E78" t="n">
-        <v>0.41</v>
+        <v>0.432</v>
       </c>
       <c r="F78" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="G78" t="b">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.2199999999999999</v>
+        <v>0.1090909090909089</v>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>327</v>
+        <v>401</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -4974,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>327</v>
+        <v>184</v>
       </c>
       <c r="P78" t="b">
         <v>0</v>
@@ -4989,50 +4989,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>CDH1</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C79" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="E79" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="F79" t="n">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="G79" t="b">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0462962962962962</v>
+        <v>-0.037673496364838</v>
       </c>
       <c r="I79" t="n">
-        <v>91</v>
+        <v>427</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.898</v>
       </c>
       <c r="L79" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="M79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>0.1157407407407408</v>
+        <v>0.2227362855254461</v>
       </c>
       <c r="O79" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -5047,53 +5047,53 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GNB1</t>
+          <t>MAK</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C80" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D80" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E80" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F80" t="n">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="G80" t="b">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0151515151515151</v>
+        <v>-0.0238095238095239</v>
       </c>
       <c r="I80" t="n">
-        <v>209</v>
+        <v>406</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.544</v>
       </c>
       <c r="L80" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="M80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0.0202020202020201</v>
+        <v>0.0238095238095237</v>
       </c>
       <c r="O80" t="n">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="P80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="b">
         <v>0</v>
@@ -5105,53 +5105,53 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TCF4</t>
+          <t>ZMYND11</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="C81" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D81" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E81" t="n">
-        <v>0.38</v>
+        <v>0.358</v>
       </c>
       <c r="F81" t="n">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="G81" t="b">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0039772727272726</v>
+        <v>0.0142857142857142</v>
       </c>
       <c r="I81" t="n">
-        <v>285</v>
+        <v>107</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.73</v>
+        <v>0.788</v>
       </c>
       <c r="L81" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="M81" t="b">
         <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0437499999999999</v>
+        <v>0.1857142857142858</v>
       </c>
       <c r="O81" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="P81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="b">
         <v>0</v>
@@ -5163,50 +5163,50 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>WDR37</t>
+          <t>MTM1</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="D82" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E82" t="n">
         <v>0.35</v>
       </c>
       <c r="F82" t="n">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="G82" t="b">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0599999999999999</v>
+        <v>-0.0035492457852706</v>
       </c>
       <c r="I82" t="n">
-        <v>66</v>
+        <v>327</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.68</v>
+        <v>0.534</v>
       </c>
       <c r="L82" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0.09999999999999989</v>
+        <v>0.0319432120674356</v>
       </c>
       <c r="O82" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -5221,53 +5221,53 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENPP1</t>
+          <t>TCF4</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E83" t="n">
-        <v>0.33</v>
+        <v>0.344</v>
       </c>
       <c r="F83" t="n">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G83" t="b">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.0056818181818182</v>
       </c>
       <c r="I83" t="n">
-        <v>43</v>
+        <v>342</v>
       </c>
       <c r="J83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="L83" t="n">
-        <v>351</v>
+        <v>33</v>
       </c>
       <c r="M83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>0.0386363636363635</v>
       </c>
       <c r="O83" t="n">
-        <v>351</v>
+        <v>30</v>
       </c>
       <c r="P83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="b">
         <v>0</v>
@@ -5279,53 +5279,53 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PPP3CA</t>
+          <t>TNPO2</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
         <v>5</v>
       </c>
       <c r="E84" t="n">
-        <v>0.31</v>
+        <v>0.336</v>
       </c>
       <c r="F84" t="n">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="G84" t="b">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.07692307692307671</v>
+        <v>-0.0333333333333333</v>
       </c>
       <c r="I84" t="n">
-        <v>52</v>
+        <v>421</v>
       </c>
       <c r="J84" t="b">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="L84" t="n">
-        <v>29</v>
+        <v>273</v>
       </c>
       <c r="M84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0.0307692307692306</v>
+        <v>0.06666666666666669</v>
       </c>
       <c r="O84" t="n">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="P84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="b">
         <v>0</v>
@@ -5337,53 +5337,53 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C1R</t>
+          <t>UBQLN2</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C85" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D85" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E85" t="n">
-        <v>0.29</v>
+        <v>0.288</v>
       </c>
       <c r="F85" t="n">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="G85" t="b">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0151515151515151</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="J85" t="b">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.75</v>
+        <v>0.8860000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="M85" t="b">
         <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>0.0075757575757576</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="O85" t="n">
-        <v>238</v>
+        <v>6</v>
       </c>
       <c r="P85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="b">
         <v>0</v>
@@ -5395,50 +5395,50 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DKC1</t>
+          <t>WNT10A</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C86" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E86" t="n">
-        <v>0.29</v>
+        <v>0.264</v>
       </c>
       <c r="F86" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G86" t="b">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0119047619047619</v>
+        <v>-0.0416666666666667</v>
       </c>
       <c r="I86" t="n">
-        <v>229</v>
+        <v>431</v>
       </c>
       <c r="J86" t="b">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.66</v>
+        <v>0.25</v>
       </c>
       <c r="L86" t="n">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0.130952380952381</v>
+        <v>0.0624999999999998</v>
       </c>
       <c r="O86" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -5466,37 +5466,37 @@
         <v>11</v>
       </c>
       <c r="E87" t="n">
-        <v>0.27</v>
+        <v>0.258</v>
       </c>
       <c r="F87" t="n">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G87" t="b">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0511363636363636</v>
+        <v>0.0454545454545454</v>
       </c>
       <c r="I87" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="J87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>0.79</v>
+        <v>0.656</v>
       </c>
       <c r="L87" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M87" t="b">
         <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>0.0568181818181817</v>
+        <v>-0.0284090909090909</v>
       </c>
       <c r="O87" t="n">
-        <v>57</v>
+        <v>398</v>
       </c>
       <c r="P87" t="b">
         <v>0</v>
@@ -5511,50 +5511,50 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FLCN</t>
+          <t>PPP3CA</t>
         </is>
       </c>
       <c r="B88" t="n">
+        <v>18</v>
+      </c>
+      <c r="C88" t="n">
         <v>13</v>
       </c>
-      <c r="C88" t="n">
-        <v>7</v>
-      </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>0.25</v>
+        <v>0.258</v>
       </c>
       <c r="F88" t="n">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="G88" t="b">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.119047619047619</v>
+        <v>0.0615384615384614</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="L88" t="n">
-        <v>357</v>
+        <v>61</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>-0.0615384615384615</v>
       </c>
       <c r="O88" t="n">
-        <v>357</v>
+        <v>438</v>
       </c>
       <c r="P88" t="b">
         <v>0</v>
@@ -5582,37 +5582,37 @@
         <v>14</v>
       </c>
       <c r="E89" t="n">
-        <v>0.25</v>
+        <v>0.232</v>
       </c>
       <c r="F89" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G89" t="b">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0064935064935065</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.9</v>
+        <v>0.8699999999999999</v>
       </c>
       <c r="L89" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="M89" t="b">
         <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>0.1363636363636363</v>
+        <v>0.1038961038961039</v>
       </c>
       <c r="O89" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -5627,53 +5627,53 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MMAB</t>
+          <t>C1R</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C90" t="n">
         <v>12</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E90" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F90" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0138888888888888</v>
+        <v>-0.0075757575757575</v>
       </c>
       <c r="I90" t="n">
-        <v>219</v>
+        <v>350</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
       <c r="L90" t="n">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="M90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>0.111111111111111</v>
+        <v>-0.0454545454545453</v>
       </c>
       <c r="O90" t="n">
-        <v>17</v>
+        <v>422</v>
       </c>
       <c r="P90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="b">
         <v>0</v>
@@ -5685,50 +5685,50 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SERPINA1</t>
+          <t>SEC23B</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D91" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>0.25</v>
+        <v>0.204</v>
       </c>
       <c r="F91" t="n">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="G91" t="b">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.024390243902439</v>
+        <v>-0.0333333333333333</v>
       </c>
       <c r="I91" t="n">
-        <v>162</v>
+        <v>420</v>
       </c>
       <c r="J91" t="b">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.65</v>
+        <v>0.1</v>
       </c>
       <c r="L91" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>0.08943089430894299</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="O91" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -5743,50 +5743,50 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GLUD1</t>
+          <t>SERPINA1</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="E92" t="n">
-        <v>0.19</v>
+        <v>0.204</v>
       </c>
       <c r="F92" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G92" t="b">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0.04</v>
+        <v>0.02710027100271</v>
       </c>
       <c r="I92" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="J92" t="b">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.32</v>
+        <v>0.5399999999999999</v>
       </c>
       <c r="L92" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0.0799999999999999</v>
+        <v>0.0433604336043359</v>
       </c>
       <c r="O92" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -5801,53 +5801,53 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PCCB</t>
+          <t>DKC1</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="C93" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E93" t="n">
-        <v>0.16</v>
+        <v>0.174</v>
       </c>
       <c r="F93" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G93" t="b">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0095238095238094</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="J93" t="b">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.92</v>
+        <v>0.514</v>
       </c>
       <c r="L93" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="M93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0.0047619047619047</v>
+        <v>0.0238095238095238</v>
       </c>
       <c r="O93" t="n">
-        <v>262</v>
+        <v>46</v>
       </c>
       <c r="P93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="b">
         <v>0</v>
@@ -5859,53 +5859,53 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SEC23B</t>
+          <t>LPAR6</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D94" t="n">
         <v>5</v>
       </c>
       <c r="E94" t="n">
-        <v>0.15</v>
+        <v>0.172</v>
       </c>
       <c r="F94" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G94" t="b">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0333333333333333</v>
+        <v>-0.057142857142857</v>
       </c>
       <c r="I94" t="n">
-        <v>124</v>
+        <v>447</v>
       </c>
       <c r="J94" t="b">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.14</v>
+        <v>0.652</v>
       </c>
       <c r="L94" t="n">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="M94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>0.0666666666666666</v>
+        <v>-0.057142857142857</v>
       </c>
       <c r="O94" t="n">
-        <v>45</v>
+        <v>435</v>
       </c>
       <c r="P94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="b">
         <v>0</v>
@@ -5917,50 +5917,50 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CYP27A1</t>
+          <t>PCCB</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C95" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D95" t="n">
         <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>0.14</v>
+        <v>0.152</v>
       </c>
       <c r="F95" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G95" t="b">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0166666666666666</v>
+        <v>-0.0095238095238094</v>
       </c>
       <c r="I95" t="n">
-        <v>199</v>
+        <v>358</v>
       </c>
       <c r="J95" t="b">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.76</v>
+        <v>0.718</v>
       </c>
       <c r="L95" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M95" t="b">
         <v>1</v>
       </c>
       <c r="N95" t="n">
-        <v>0.0166666666666667</v>
+        <v>-0.09523809523809521</v>
       </c>
       <c r="O95" t="n">
-        <v>169</v>
+        <v>456</v>
       </c>
       <c r="P95" t="b">
         <v>0</v>
@@ -5975,50 +5975,50 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DBT</t>
+          <t>SLC1A2</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C96" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="E96" t="n">
-        <v>0.14</v>
+        <v>0.126</v>
       </c>
       <c r="F96" t="n">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="G96" t="b">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0078125</v>
+        <v>-0.0148809523809523</v>
       </c>
       <c r="I96" t="n">
-        <v>254</v>
+        <v>378</v>
       </c>
       <c r="J96" t="b">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.86</v>
+        <v>0.608</v>
       </c>
       <c r="L96" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="M96" t="b">
         <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>0.0390625</v>
+        <v>-0.07142857142857149</v>
       </c>
       <c r="O96" t="n">
-        <v>95</v>
+        <v>444</v>
       </c>
       <c r="P96" t="b">
         <v>0</v>
@@ -6033,50 +6033,50 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SNAP25</t>
+          <t>EYA1</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C97" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E97" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F97" t="n">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="G97" t="b">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0514705882352941</v>
+        <v>0.017094017094017</v>
       </c>
       <c r="I97" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="J97" t="b">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.49</v>
+        <v>0.336</v>
       </c>
       <c r="L97" t="n">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0.0661764705882352</v>
+        <v>0.0512820512820513</v>
       </c>
       <c r="O97" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -6091,50 +6091,50 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KARS1</t>
+          <t>DBT</t>
         </is>
       </c>
       <c r="B98" t="n">
+        <v>24</v>
+      </c>
+      <c r="C98" t="n">
         <v>16</v>
       </c>
-      <c r="C98" t="n">
-        <v>9</v>
-      </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E98" t="n">
-        <v>0.12</v>
+        <v>0.112</v>
       </c>
       <c r="F98" t="n">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="G98" t="b">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0634920634920636</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="J98" t="b">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.95</v>
+        <v>0.6859999999999999</v>
       </c>
       <c r="L98" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M98" t="b">
         <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>0.0158730158730159</v>
+        <v>-0.046875</v>
       </c>
       <c r="O98" t="n">
-        <v>178</v>
+        <v>423</v>
       </c>
       <c r="P98" t="b">
         <v>0</v>
@@ -6149,50 +6149,50 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ANOS1</t>
+          <t>AIFM1</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E99" t="n">
-        <v>0.08</v>
+        <v>0.098</v>
       </c>
       <c r="F99" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="G99" t="b">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0428571428571428</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>99</v>
+        <v>158</v>
       </c>
       <c r="J99" t="b">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.38</v>
+        <v>0.634</v>
       </c>
       <c r="L99" t="n">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="M99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>0.0857142857142857</v>
+        <v>0.025</v>
       </c>
       <c r="O99" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -6207,53 +6207,53 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FOXF1</t>
+          <t>ANOS1</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C100" t="n">
+        <v>7</v>
+      </c>
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="F100" t="n">
+        <v>313</v>
+      </c>
+      <c r="G100" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.0285714285714285</v>
+      </c>
+      <c r="I100" t="n">
+        <v>67</v>
+      </c>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L100" t="n">
+        <v>150</v>
+      </c>
+      <c r="M100" t="b">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.07142857142857149</v>
+      </c>
+      <c r="O100" t="n">
         <v>12</v>
       </c>
-      <c r="D100" t="n">
-        <v>6</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F100" t="n">
-        <v>299</v>
-      </c>
-      <c r="G100" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0.0138888888888888</v>
-      </c>
-      <c r="I100" t="n">
-        <v>217</v>
-      </c>
-      <c r="J100" t="b">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="L100" t="n">
-        <v>46</v>
-      </c>
-      <c r="M100" t="b">
-        <v>1</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0.0138888888888888</v>
-      </c>
-      <c r="O100" t="n">
-        <v>193</v>
-      </c>
       <c r="P100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" t="b">
         <v>0</v>
@@ -6265,53 +6265,53 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LPAR6</t>
+          <t>ATP6V1B2</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>12</v>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="G101" t="b">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="J101" t="b">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0.77</v>
+        <v>0.074</v>
       </c>
       <c r="L101" t="n">
-        <v>35</v>
+        <v>301</v>
       </c>
       <c r="M101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>0.0285714285714286</v>
+        <v>0.0277777777777777</v>
       </c>
       <c r="O101" t="n">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="P101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" t="b">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="G102" t="b">
         <v>0</v>
@@ -6348,25 +6348,25 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>344</v>
+        <v>177</v>
       </c>
       <c r="J102" t="b">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0.36</v>
+        <v>0.3259999999999999</v>
       </c>
       <c r="L102" t="n">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="O102" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -6381,23 +6381,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FA2H</t>
+          <t>IL11RA</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C103" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="G103" t="b">
         <v>0</v>
@@ -6406,28 +6406,28 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>359</v>
+        <v>222</v>
       </c>
       <c r="J103" t="b">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>0.34</v>
+        <v>0.6980000000000001</v>
       </c>
       <c r="L103" t="n">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="M103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N103" t="n">
-        <v>0.0972222222222222</v>
+        <v>-1.110223024625156e-16</v>
       </c>
       <c r="O103" t="n">
-        <v>25</v>
+        <v>266</v>
       </c>
       <c r="P103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="b">
         <v>0</v>
@@ -6439,14 +6439,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FARSB</t>
+          <t>PRMT7</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
         <v>5</v>
@@ -6455,7 +6455,7 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>360</v>
+        <v>427</v>
       </c>
       <c r="G104" t="b">
         <v>0</v>
@@ -6464,25 +6464,25 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>360</v>
+        <v>251</v>
       </c>
       <c r="J104" t="b">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0.65</v>
+        <v>0.452</v>
       </c>
       <c r="L104" t="n">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0.06666666666666669</v>
+        <v>0.0399999999999999</v>
       </c>
       <c r="O104" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -6497,23 +6497,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HGD</t>
+          <t>RARS1</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C105" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D105" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>379</v>
+        <v>431</v>
       </c>
       <c r="G105" t="b">
         <v>0</v>
@@ -6522,28 +6522,28 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>379</v>
+        <v>254</v>
       </c>
       <c r="J105" t="b">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7699999999999999</v>
       </c>
       <c r="L105" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="M105" t="b">
         <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>0.0122448979591835</v>
+        <v>0.1714285714285714</v>
       </c>
       <c r="O105" t="n">
-        <v>209</v>
+        <v>4</v>
       </c>
       <c r="P105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" t="b">
         <v>0</v>
@@ -6555,51 +6555,51 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HSD17B10</t>
+          <t>XPC</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" t="n">
+        <v>11</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>465</v>
+      </c>
+      <c r="G106" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>290</v>
+      </c>
+      <c r="J106" t="b">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="L106" t="n">
+        <v>12</v>
+      </c>
+      <c r="M106" t="b">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.0909090909090908</v>
+      </c>
+      <c r="O106" t="n">
         <v>10</v>
       </c>
-      <c r="D106" t="n">
-        <v>5</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>385</v>
-      </c>
-      <c r="G106" t="b">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>385</v>
-      </c>
-      <c r="J106" t="b">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L106" t="n">
-        <v>37</v>
-      </c>
-      <c r="M106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0.09999999999999989</v>
-      </c>
-      <c r="O106" t="n">
-        <v>22</v>
-      </c>
       <c r="P106" t="b">
         <v>1</v>
       </c>
@@ -6607,354 +6607,6 @@
         <v>0</v>
       </c>
       <c r="R106" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>IL11RA</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>10</v>
-      </c>
-      <c r="C107" t="n">
-        <v>5</v>
-      </c>
-      <c r="D107" t="n">
-        <v>5</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>386</v>
-      </c>
-      <c r="G107" t="b">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>386</v>
-      </c>
-      <c r="J107" t="b">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="L107" t="n">
-        <v>24</v>
-      </c>
-      <c r="M107" t="b">
-        <v>1</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0.1599999999999999</v>
-      </c>
-      <c r="O107" t="n">
-        <v>10</v>
-      </c>
-      <c r="P107" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q107" t="b">
-        <v>0</v>
-      </c>
-      <c r="R107" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>PRMT7</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>10</v>
-      </c>
-      <c r="C108" t="n">
-        <v>5</v>
-      </c>
-      <c r="D108" t="n">
-        <v>5</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>418</v>
-      </c>
-      <c r="G108" t="b">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>418</v>
-      </c>
-      <c r="J108" t="b">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L108" t="n">
-        <v>77</v>
-      </c>
-      <c r="M108" t="b">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0.1999999999999999</v>
-      </c>
-      <c r="O108" t="n">
-        <v>5</v>
-      </c>
-      <c r="P108" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q108" t="b">
-        <v>0</v>
-      </c>
-      <c r="R108" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>RARS1</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>12</v>
-      </c>
-      <c r="C109" t="n">
-        <v>7</v>
-      </c>
-      <c r="D109" t="n">
-        <v>5</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>422</v>
-      </c>
-      <c r="G109" t="b">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>422</v>
-      </c>
-      <c r="J109" t="b">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L109" t="n">
-        <v>20</v>
-      </c>
-      <c r="M109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N109" t="n">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="O109" t="n">
-        <v>4</v>
-      </c>
-      <c r="P109" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q109" t="b">
-        <v>0</v>
-      </c>
-      <c r="R109" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>SELENON</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>13</v>
-      </c>
-      <c r="C110" t="n">
-        <v>5</v>
-      </c>
-      <c r="D110" t="n">
-        <v>8</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>428</v>
-      </c>
-      <c r="G110" t="b">
-        <v>0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="n">
-        <v>428</v>
-      </c>
-      <c r="J110" t="b">
-        <v>0</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="L110" t="n">
-        <v>13</v>
-      </c>
-      <c r="M110" t="b">
-        <v>1</v>
-      </c>
-      <c r="N110" t="n">
-        <v>1.110223024625156e-16</v>
-      </c>
-      <c r="O110" t="n">
-        <v>311</v>
-      </c>
-      <c r="P110" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="b">
-        <v>0</v>
-      </c>
-      <c r="R110" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>UBQLN2</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>11</v>
-      </c>
-      <c r="C111" t="n">
-        <v>5</v>
-      </c>
-      <c r="D111" t="n">
-        <v>6</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>460</v>
-      </c>
-      <c r="G111" t="b">
-        <v>0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="n">
-        <v>460</v>
-      </c>
-      <c r="J111" t="b">
-        <v>0</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L111" t="n">
-        <v>15</v>
-      </c>
-      <c r="M111" t="b">
-        <v>1</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0.1999999999999999</v>
-      </c>
-      <c r="O111" t="n">
-        <v>6</v>
-      </c>
-      <c r="P111" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q111" t="b">
-        <v>0</v>
-      </c>
-      <c r="R111" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>XPC</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>5</v>
-      </c>
-      <c r="D112" t="n">
-        <v>11</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>465</v>
-      </c>
-      <c r="G112" t="b">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>465</v>
-      </c>
-      <c r="J112" t="b">
-        <v>0</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L112" t="n">
-        <v>21</v>
-      </c>
-      <c r="M112" t="b">
-        <v>1</v>
-      </c>
-      <c r="N112" t="n">
-        <v>0.1454545454545454</v>
-      </c>
-      <c r="O112" t="n">
-        <v>11</v>
-      </c>
-      <c r="P112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q112" t="b">
-        <v>0</v>
-      </c>
-      <c r="R112" t="b">
         <v>0</v>
       </c>
     </row>
